--- a/gstdatabase/GSTR-1-2019-2020.xlsx
+++ b/gstdatabase/GSTR-1-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EBA763-5FD2-4412-BE5B-5FC541D0ED28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91033FD-3306-4640-96BB-AF449BC7DBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -411,17 +411,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -746,11 +746,11 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -786,7 +786,7 @@
       <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="30">
@@ -796,87 +796,87 @@
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
       <c r="G7" s="32"/>
-      <c r="H7" s="25">
+      <c r="H7" s="23">
         <v>43586</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="25">
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="23">
         <v>43617</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="25">
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="23">
         <v>43647</v>
       </c>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="25">
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="23">
         <v>43678</v>
       </c>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="25">
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="23">
         <v>43709</v>
       </c>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="25">
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="23">
         <v>43739</v>
       </c>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="26"/>
-      <c r="AJ7" s="26"/>
-      <c r="AK7" s="26"/>
-      <c r="AL7" s="25">
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
+      <c r="AJ7" s="24"/>
+      <c r="AK7" s="24"/>
+      <c r="AL7" s="23">
         <v>43770</v>
       </c>
-      <c r="AM7" s="26"/>
-      <c r="AN7" s="26"/>
-      <c r="AO7" s="26"/>
-      <c r="AP7" s="26"/>
-      <c r="AQ7" s="25">
+      <c r="AM7" s="24"/>
+      <c r="AN7" s="24"/>
+      <c r="AO7" s="24"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="23">
         <v>43800</v>
       </c>
-      <c r="AR7" s="26"/>
-      <c r="AS7" s="26"/>
-      <c r="AT7" s="26"/>
-      <c r="AU7" s="26"/>
-      <c r="AV7" s="25">
+      <c r="AR7" s="24"/>
+      <c r="AS7" s="24"/>
+      <c r="AT7" s="24"/>
+      <c r="AU7" s="24"/>
+      <c r="AV7" s="23">
         <v>43831</v>
       </c>
-      <c r="AW7" s="26"/>
-      <c r="AX7" s="26"/>
-      <c r="AY7" s="26"/>
-      <c r="AZ7" s="26"/>
-      <c r="BA7" s="25">
+      <c r="AW7" s="24"/>
+      <c r="AX7" s="24"/>
+      <c r="AY7" s="24"/>
+      <c r="AZ7" s="24"/>
+      <c r="BA7" s="23">
         <v>43862</v>
       </c>
-      <c r="BB7" s="26"/>
-      <c r="BC7" s="26"/>
-      <c r="BD7" s="26"/>
-      <c r="BE7" s="26"/>
-      <c r="BF7" s="25">
+      <c r="BB7" s="24"/>
+      <c r="BC7" s="24"/>
+      <c r="BD7" s="24"/>
+      <c r="BE7" s="24"/>
+      <c r="BF7" s="23">
         <v>43891</v>
       </c>
-      <c r="BG7" s="26"/>
-      <c r="BH7" s="26"/>
-      <c r="BI7" s="26"/>
-      <c r="BJ7" s="26"/>
+      <c r="BG7" s="24"/>
+      <c r="BH7" s="24"/>
+      <c r="BI7" s="24"/>
+      <c r="BJ7" s="24"/>
     </row>
     <row r="8" spans="1:62" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="29"/>
-      <c r="B8" s="26"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="22" t="s">
         <v>3</v>
       </c>
@@ -1209,14 +1209,14 @@
       </c>
       <c r="AS9" s="6">
         <f>AT9-AR9</f>
-        <v>48897</v>
+        <v>48898</v>
       </c>
       <c r="AT9" s="15">
-        <v>73781</v>
+        <v>73782</v>
       </c>
       <c r="AU9" s="7">
         <f>AT9/AQ9</f>
-        <v>0.80027984467535851</v>
+        <v>0.80029069136820186</v>
       </c>
       <c r="AV9" s="13">
         <v>39353</v>
@@ -1243,14 +1243,14 @@
       </c>
       <c r="BC9" s="6">
         <f>BD9-BB9</f>
-        <v>13822</v>
+        <v>13823</v>
       </c>
       <c r="BD9" s="14">
-        <v>27517</v>
+        <v>27518</v>
       </c>
       <c r="BE9" s="7">
         <f>BD9/BA9</f>
-        <v>0.69992877855216973</v>
+        <v>0.6999542147835377</v>
       </c>
       <c r="BF9" s="13">
         <v>85741</v>
@@ -1260,14 +1260,14 @@
       </c>
       <c r="BH9" s="6">
         <f>BI9-BG9</f>
-        <v>37507</v>
+        <v>37508</v>
       </c>
       <c r="BI9" s="15">
-        <v>71539</v>
+        <v>71540</v>
       </c>
       <c r="BJ9" s="7">
         <f>BI9/BF9</f>
-        <v>0.83436162396053226</v>
+        <v>0.8343732869922208</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.3">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="BC10" s="6">
         <f t="shared" ref="BC10:BC46" si="20">BD10-BB10</f>
-        <v>4135</v>
+        <v>4136</v>
       </c>
       <c r="BD10" s="14">
-        <v>18993</v>
+        <v>18994</v>
       </c>
       <c r="BE10" s="7">
         <f t="shared" ref="BE10:BE46" si="21">BD10/BA10</f>
-        <v>0.82092842323651449</v>
+        <v>0.82097164591977867</v>
       </c>
       <c r="BF10" s="13">
         <v>86286</v>
@@ -1472,14 +1472,14 @@
       </c>
       <c r="BH10" s="6">
         <f t="shared" ref="BH10:BH46" si="22">BI10-BG10</f>
-        <v>21751</v>
+        <v>21753</v>
       </c>
       <c r="BI10" s="15">
-        <v>78852</v>
+        <v>78854</v>
       </c>
       <c r="BJ10" s="7">
         <f t="shared" ref="BJ10:BJ46" si="23">BI10/BF10</f>
-        <v>0.91384465614352273</v>
+        <v>0.91386783487471901</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="O11" s="6">
         <f t="shared" si="4"/>
-        <v>98779</v>
+        <v>98780</v>
       </c>
       <c r="P11" s="15">
-        <v>279247</v>
+        <v>279248</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="5"/>
-        <v>0.9040777013354917</v>
+        <v>0.90408093889113716</v>
       </c>
       <c r="R11" s="13">
         <v>109710</v>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="T11" s="6">
         <f t="shared" si="6"/>
-        <v>37777</v>
+        <v>37778</v>
       </c>
       <c r="U11" s="14">
-        <v>80674</v>
+        <v>80675</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" si="7"/>
-        <v>0.73533861999817696</v>
+        <v>0.73534773493756267</v>
       </c>
       <c r="W11" s="13">
         <v>106470</v>
@@ -1582,14 +1582,14 @@
       </c>
       <c r="AD11" s="6">
         <f t="shared" si="10"/>
-        <v>145907</v>
+        <v>145909</v>
       </c>
       <c r="AE11" s="15">
-        <v>283051</v>
+        <v>283053</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="11"/>
-        <v>0.90987145157816574</v>
+        <v>0.90987788060651453</v>
       </c>
       <c r="AG11" s="13">
         <v>101504</v>
@@ -1633,14 +1633,14 @@
       </c>
       <c r="AS11" s="6">
         <f t="shared" si="16"/>
-        <v>60442</v>
+        <v>60444</v>
       </c>
       <c r="AT11" s="15">
-        <v>286178</v>
+        <v>286180</v>
       </c>
       <c r="AU11" s="7">
         <f t="shared" si="17"/>
-        <v>0.92740594790961151</v>
+        <v>0.92741242923206046</v>
       </c>
       <c r="AV11" s="13">
         <v>95635</v>
@@ -1684,14 +1684,14 @@
       </c>
       <c r="BH11" s="6">
         <f t="shared" si="22"/>
-        <v>52704</v>
+        <v>52707</v>
       </c>
       <c r="BI11" s="15">
-        <v>286767</v>
+        <v>286770</v>
       </c>
       <c r="BJ11" s="7">
         <f t="shared" si="23"/>
-        <v>0.91855384792789097</v>
+        <v>0.91856345733742484</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>21651</v>
+        <v>21652</v>
       </c>
       <c r="F13" s="14">
-        <v>30727</v>
+        <v>30728</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="1"/>
-        <v>0.48096609585824751</v>
+        <v>0.48098174873994304</v>
       </c>
       <c r="H13" s="13">
         <v>59731</v>
@@ -1938,14 +1938,14 @@
       </c>
       <c r="J13" s="6">
         <f t="shared" si="2"/>
-        <v>21940</v>
+        <v>21941</v>
       </c>
       <c r="K13" s="14">
-        <v>30923</v>
+        <v>30924</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="3"/>
-        <v>0.51770437461284757</v>
+        <v>0.5177211163382498</v>
       </c>
       <c r="M13" s="13">
         <v>129422</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="O13" s="6">
         <f t="shared" si="4"/>
-        <v>68079</v>
+        <v>68082</v>
       </c>
       <c r="P13" s="15">
-        <v>110027</v>
+        <v>110030</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="5"/>
-        <v>0.85014139790762</v>
+        <v>0.85016457789247579</v>
       </c>
       <c r="R13" s="13">
         <v>54062</v>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="T13" s="6">
         <f t="shared" si="6"/>
-        <v>22611</v>
+        <v>22612</v>
       </c>
       <c r="U13" s="14">
-        <v>31333</v>
+        <v>31334</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="7"/>
-        <v>0.57957530243054267</v>
+        <v>0.57959379971144243</v>
       </c>
       <c r="W13" s="13">
         <v>51426</v>
@@ -1989,14 +1989,14 @@
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="8"/>
-        <v>22437</v>
+        <v>22438</v>
       </c>
       <c r="Z13" s="14">
-        <v>31586</v>
+        <v>31587</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="9"/>
-        <v>0.61420293236884071</v>
+        <v>0.614222377785556</v>
       </c>
       <c r="AB13" s="13">
         <v>131532</v>
@@ -2006,14 +2006,14 @@
       </c>
       <c r="AD13" s="6">
         <f t="shared" si="10"/>
-        <v>76401</v>
+        <v>76403</v>
       </c>
       <c r="AE13" s="15">
-        <v>113207</v>
+        <v>113209</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="11"/>
-        <v>0.86068029072773167</v>
+        <v>0.86069549615302743</v>
       </c>
       <c r="AG13" s="13">
         <v>48183</v>
@@ -2057,14 +2057,14 @@
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="16"/>
-        <v>42778</v>
+        <v>42779</v>
       </c>
       <c r="AT13" s="15">
-        <v>115605</v>
+        <v>115606</v>
       </c>
       <c r="AU13" s="7">
         <f t="shared" si="17"/>
-        <v>0.89994395055193133</v>
+        <v>0.89995173519749649</v>
       </c>
       <c r="AV13" s="13">
         <v>43497</v>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="BH13" s="6">
         <f t="shared" si="22"/>
-        <v>38738</v>
+        <v>38739</v>
       </c>
       <c r="BI13" s="15">
-        <v>114891</v>
+        <v>114892</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" si="23"/>
-        <v>0.87188574290636167</v>
+        <v>0.87189333171438765</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="O14" s="6">
         <f t="shared" si="4"/>
-        <v>167145</v>
+        <v>167146</v>
       </c>
       <c r="P14" s="15">
-        <v>370936</v>
+        <v>370937</v>
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="5"/>
-        <v>0.87533627207596676</v>
+        <v>0.87533863188000871</v>
       </c>
       <c r="R14" s="13">
         <v>173026</v>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>63305</v>
+        <v>63306</v>
       </c>
       <c r="Z14" s="14">
-        <v>120655</v>
+        <v>120656</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="9"/>
-        <v>0.72321257312745757</v>
+        <v>0.72321856718135613</v>
       </c>
       <c r="AB14" s="13">
         <v>423483</v>
@@ -2218,14 +2218,14 @@
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>215078</v>
+        <v>215079</v>
       </c>
       <c r="AE14" s="15">
-        <v>377603</v>
+        <v>377604</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="11"/>
-        <v>0.89166035000224331</v>
+        <v>0.89166271137212116</v>
       </c>
       <c r="AG14" s="13">
         <v>160277</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>103994</v>
+        <v>103996</v>
       </c>
       <c r="AT14" s="15">
-        <v>383965</v>
+        <v>383967</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.90463265974465357</v>
+        <v>0.9046373718025742</v>
       </c>
       <c r="AV14" s="13">
         <v>153606</v>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>88265</v>
+        <v>88266</v>
       </c>
       <c r="BI14" s="15">
-        <v>383344</v>
+        <v>383345</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.90549921932391797</v>
+        <v>0.90550158143006632</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2396,14 +2396,14 @@
       </c>
       <c r="T15" s="6">
         <f t="shared" si="6"/>
-        <v>103183</v>
+        <v>103184</v>
       </c>
       <c r="U15" s="14">
-        <v>173208</v>
+        <v>173209</v>
       </c>
       <c r="V15" s="7">
         <f t="shared" si="7"/>
-        <v>0.53619123683575098</v>
+        <v>0.53619433248512538</v>
       </c>
       <c r="W15" s="13">
         <v>309950</v>
@@ -2557,14 +2557,14 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>70976</v>
+        <v>70977</v>
       </c>
       <c r="F16" s="14">
-        <v>122154</v>
+        <v>122155</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>0.49555777328822143</v>
+        <v>0.4955618301162687</v>
       </c>
       <c r="H16" s="13">
         <v>236220</v>
@@ -2574,14 +2574,14 @@
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>67812</v>
+        <v>67813</v>
       </c>
       <c r="K16" s="14">
-        <v>122239</v>
+        <v>122240</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="3"/>
-        <v>0.51747946829226987</v>
+        <v>0.51748370163406998</v>
       </c>
       <c r="M16" s="13">
         <v>560439</v>
@@ -2608,14 +2608,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>72875</v>
+        <v>72876</v>
       </c>
       <c r="U16" s="14">
-        <v>123840</v>
+        <v>123841</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.60170833859698558</v>
+        <v>0.6017131973529497</v>
       </c>
       <c r="W16" s="13">
         <v>193923</v>
@@ -2625,14 +2625,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>69748</v>
+        <v>69749</v>
       </c>
       <c r="Z16" s="14">
-        <v>123968</v>
+        <v>123969</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.63926403778819429</v>
+        <v>0.63926919447409536</v>
       </c>
       <c r="AB16" s="13">
         <v>559918</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>300040</v>
+        <v>300041</v>
       </c>
       <c r="AE16" s="15">
-        <v>499303</v>
+        <v>499304</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.89174307666479735</v>
+        <v>0.89174486264060093</v>
       </c>
       <c r="AG16" s="13">
         <v>184413</v>
@@ -2659,14 +2659,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>81879</v>
+        <v>81880</v>
       </c>
       <c r="AJ16" s="14">
-        <v>125173</v>
+        <v>125174</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.6787645122632352</v>
+        <v>0.67876993487443948</v>
       </c>
       <c r="AL16" s="13">
         <v>173833</v>
@@ -2676,14 +2676,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>72250</v>
+        <v>72251</v>
       </c>
       <c r="AO16" s="14">
-        <v>127961</v>
+        <v>127962</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.73611454672012799</v>
+        <v>0.736120299367784</v>
       </c>
       <c r="AQ16" s="13">
         <v>541872</v>
@@ -2693,14 +2693,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>139196</v>
+        <v>139198</v>
       </c>
       <c r="AT16" s="15">
-        <v>507939</v>
+        <v>507941</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.93737820001771632</v>
+        <v>0.93738189092627044</v>
       </c>
       <c r="AV16" s="13">
         <v>152784</v>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>47568</v>
+        <v>47569</v>
       </c>
       <c r="AY16" s="14">
-        <v>126487</v>
+        <v>126488</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.82788119174782704</v>
+        <v>0.82788773693580475</v>
       </c>
       <c r="BA16" s="13">
         <v>150750</v>
@@ -2727,14 +2727,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>24129</v>
+        <v>24130</v>
       </c>
       <c r="BD16" s="14">
-        <v>126197</v>
+        <v>126198</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.83712769485903815</v>
+        <v>0.837134328358209</v>
       </c>
       <c r="BF16" s="13">
         <v>552190</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>134288</v>
+        <v>134291</v>
       </c>
       <c r="BI16" s="15">
-        <v>511743</v>
+        <v>511746</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.92675166156576538</v>
+        <v>0.92675709447834986</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2803,14 +2803,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>588938</v>
+        <v>588940</v>
       </c>
       <c r="P17" s="15">
-        <v>956756</v>
+        <v>956758</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.85524905536579932</v>
+        <v>0.85525084317597322</v>
       </c>
       <c r="R17" s="13">
         <v>453407</v>
@@ -2854,14 +2854,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>697987</v>
+        <v>697990</v>
       </c>
       <c r="AE17" s="15">
-        <v>983321</v>
+        <v>983324</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.87319224737639434</v>
+        <v>0.87319491138615535</v>
       </c>
       <c r="AG17" s="13">
         <v>411675</v>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>224658</v>
+        <v>224659</v>
       </c>
       <c r="AO17" s="14">
-        <v>307345</v>
+        <v>307346</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.78446962252448393</v>
+        <v>0.78447217493178689</v>
       </c>
       <c r="AQ17" s="13">
         <v>1127354</v>
@@ -2905,14 +2905,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>381277</v>
+        <v>381281</v>
       </c>
       <c r="AT17" s="15">
-        <v>1005700</v>
+        <v>1005704</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.89208890907381355</v>
+        <v>0.89209245720510155</v>
       </c>
       <c r="AV17" s="13">
         <v>386848</v>
@@ -2922,14 +2922,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>170743</v>
+        <v>170745</v>
       </c>
       <c r="AY17" s="14">
-        <v>308733</v>
+        <v>308735</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.79807314500785842</v>
+        <v>0.7980783149971048</v>
       </c>
       <c r="BA17" s="13">
         <v>379844</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>93342</v>
+        <v>93343</v>
       </c>
       <c r="BD17" s="14">
-        <v>308648</v>
+        <v>308649</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.81256515832815579</v>
+        <v>0.81256779098787923</v>
       </c>
       <c r="BF17" s="13">
         <v>1155076</v>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>370545</v>
+        <v>370551</v>
       </c>
       <c r="BI17" s="15">
-        <v>1003178</v>
+        <v>1003184</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.8684952332140915</v>
+        <v>0.86850042767748614</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -4058,14 +4058,14 @@
       </c>
       <c r="J23" s="6">
         <f t="shared" si="2"/>
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="K23" s="14">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="3"/>
-        <v>0.60871580899397315</v>
+        <v>0.60894761242466389</v>
       </c>
       <c r="M23" s="13">
         <v>5454</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" si="4"/>
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="P23" s="15">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="Q23" s="7">
         <f t="shared" si="5"/>
-        <v>0.73395672900623399</v>
+        <v>0.73414008067473413</v>
       </c>
       <c r="R23" s="13">
         <v>4339</v>
@@ -4092,14 +4092,14 @@
       </c>
       <c r="T23" s="6">
         <f t="shared" si="6"/>
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="U23" s="14">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="7"/>
-        <v>0.6252592763309518</v>
+        <v>0.62548974418068681</v>
       </c>
       <c r="W23" s="13">
         <v>4331</v>
@@ -4109,14 +4109,14 @@
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="8"/>
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="Z23" s="14">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="9"/>
-        <v>0.63033941353036249</v>
+        <v>0.6305703070884322</v>
       </c>
       <c r="AB23" s="13">
         <v>5800</v>
@@ -4126,14 +4126,14 @@
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="AE23" s="15">
-        <v>4172</v>
+        <v>4173</v>
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="11"/>
-        <v>0.71931034482758616</v>
+        <v>0.71948275862068967</v>
       </c>
       <c r="AG23" s="13">
         <v>4378</v>
@@ -4143,14 +4143,14 @@
       </c>
       <c r="AI23" s="6">
         <f t="shared" si="12"/>
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="AJ23" s="14">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="13"/>
-        <v>0.62745545911375056</v>
+        <v>0.62768387391502967</v>
       </c>
       <c r="AL23" s="13">
         <v>4406</v>
@@ -4160,14 +4160,14 @@
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="14"/>
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AO23" s="14">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="AP23" s="7">
         <f t="shared" si="15"/>
-        <v>0.63504312301407173</v>
+        <v>0.6352700862460281</v>
       </c>
       <c r="AQ23" s="13">
         <v>6083</v>
@@ -4177,14 +4177,14 @@
       </c>
       <c r="AS23" s="6">
         <f t="shared" si="16"/>
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="AT23" s="15">
-        <v>4309</v>
+        <v>4310</v>
       </c>
       <c r="AU23" s="7">
         <f t="shared" si="17"/>
-        <v>0.70836758178530335</v>
+        <v>0.70853197435475912</v>
       </c>
       <c r="AV23" s="13">
         <v>4479</v>
@@ -4194,14 +4194,14 @@
       </c>
       <c r="AX23" s="6">
         <f t="shared" si="18"/>
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="AY23" s="14">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="19"/>
-        <v>0.64233087742799733</v>
+        <v>0.64255414154945301</v>
       </c>
       <c r="BA23" s="13">
         <v>4501</v>
@@ -4211,14 +4211,14 @@
       </c>
       <c r="BC23" s="6">
         <f t="shared" si="20"/>
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="BD23" s="14">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="21"/>
-        <v>0.64274605643190397</v>
+        <v>0.64296822928238173</v>
       </c>
       <c r="BF23" s="13">
         <v>6256</v>
@@ -4228,14 +4228,14 @@
       </c>
       <c r="BH23" s="6">
         <f t="shared" si="22"/>
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="BI23" s="15">
-        <v>4439</v>
+        <v>4440</v>
       </c>
       <c r="BJ23" s="7">
         <f t="shared" si="23"/>
-        <v>0.7095588235294118</v>
+        <v>0.70971867007672629</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="AS24" s="6">
         <f t="shared" si="16"/>
-        <v>9379</v>
+        <v>9380</v>
       </c>
       <c r="AT24" s="15">
-        <v>20268</v>
+        <v>20269</v>
       </c>
       <c r="AU24" s="7">
         <f t="shared" si="17"/>
-        <v>0.82790735672562399</v>
+        <v>0.82794820473019892</v>
       </c>
       <c r="AV24" s="13">
         <v>10298</v>
@@ -4440,14 +4440,14 @@
       </c>
       <c r="BH24" s="6">
         <f t="shared" si="22"/>
-        <v>7537</v>
+        <v>7538</v>
       </c>
       <c r="BI24" s="15">
-        <v>20230</v>
+        <v>20231</v>
       </c>
       <c r="BJ24" s="7">
         <f t="shared" si="23"/>
-        <v>0.83577773187357984</v>
+        <v>0.83581904565172482</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="E25" s="6">
         <f t="shared" si="0"/>
-        <v>6510</v>
+        <v>6512</v>
       </c>
       <c r="F25" s="14">
-        <v>7901</v>
+        <v>7903</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="1"/>
-        <v>0.47902267491208922</v>
+        <v>0.47914393112647025</v>
       </c>
       <c r="H25" s="13">
         <v>16584</v>
@@ -4482,14 +4482,14 @@
       </c>
       <c r="J25" s="6">
         <f t="shared" si="2"/>
-        <v>6409</v>
+        <v>6411</v>
       </c>
       <c r="K25" s="14">
-        <v>8004</v>
+        <v>8006</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="3"/>
-        <v>0.48263386396526775</v>
+        <v>0.4827544621321756</v>
       </c>
       <c r="M25" s="13">
         <v>24878</v>
@@ -4499,14 +4499,14 @@
       </c>
       <c r="O25" s="6">
         <f t="shared" si="4"/>
-        <v>11580</v>
+        <v>11584</v>
       </c>
       <c r="P25" s="15">
-        <v>17319</v>
+        <v>17323</v>
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="5"/>
-        <v>0.69615724736715168</v>
+        <v>0.69631803199614117</v>
       </c>
       <c r="R25" s="13">
         <v>16556</v>
@@ -4516,14 +4516,14 @@
       </c>
       <c r="T25" s="6">
         <f t="shared" si="6"/>
-        <v>6773</v>
+        <v>6776</v>
       </c>
       <c r="U25" s="14">
-        <v>8318</v>
+        <v>8321</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="7"/>
-        <v>0.50241604252234839</v>
+        <v>0.50259724571152453</v>
       </c>
       <c r="W25" s="13">
         <v>16201</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="Y25" s="6">
         <f t="shared" si="8"/>
-        <v>6530</v>
+        <v>6532</v>
       </c>
       <c r="Z25" s="14">
-        <v>8359</v>
+        <v>8361</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="9"/>
-        <v>0.51595580519721007</v>
+        <v>0.51607925436701441</v>
       </c>
       <c r="AB25" s="13">
         <v>26140</v>
@@ -4550,14 +4550,14 @@
       </c>
       <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>12093</v>
+        <v>12099</v>
       </c>
       <c r="AE25" s="15">
-        <v>18086</v>
+        <v>18092</v>
       </c>
       <c r="AF25" s="7">
         <f t="shared" si="11"/>
-        <v>0.69188982402448351</v>
+        <v>0.69211935730680951</v>
       </c>
       <c r="AG25" s="13">
         <v>16090</v>
@@ -4567,14 +4567,14 @@
       </c>
       <c r="AI25" s="6">
         <f t="shared" si="12"/>
-        <v>6888</v>
+        <v>6891</v>
       </c>
       <c r="AJ25" s="14">
-        <v>8412</v>
+        <v>8415</v>
       </c>
       <c r="AK25" s="7">
         <f t="shared" si="13"/>
-        <v>0.52280919825978867</v>
+        <v>0.52299564947172161</v>
       </c>
       <c r="AL25" s="13">
         <v>15981</v>
@@ -4584,14 +4584,14 @@
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="14"/>
-        <v>6630</v>
+        <v>6632</v>
       </c>
       <c r="AO25" s="14">
-        <v>8377</v>
+        <v>8379</v>
       </c>
       <c r="AP25" s="7">
         <f t="shared" si="15"/>
-        <v>0.52418496965146111</v>
+        <v>0.52431011826544016</v>
       </c>
       <c r="AQ25" s="13">
         <v>26428</v>
@@ -4601,14 +4601,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>10635</v>
+        <v>10639</v>
       </c>
       <c r="AT25" s="15">
-        <v>17991</v>
+        <v>17995</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.68075525957317995</v>
+        <v>0.68090661419706378</v>
       </c>
       <c r="AV25" s="13">
         <v>15911</v>
@@ -4618,14 +4618,14 @@
       </c>
       <c r="AX25" s="6">
         <f t="shared" si="18"/>
-        <v>6037</v>
+        <v>6039</v>
       </c>
       <c r="AY25" s="14">
-        <v>8514</v>
+        <v>8516</v>
       </c>
       <c r="AZ25" s="7">
         <f t="shared" si="19"/>
-        <v>0.53510150210546159</v>
+        <v>0.53522720130727175</v>
       </c>
       <c r="BA25" s="13">
         <v>15896</v>
@@ -4635,14 +4635,14 @@
       </c>
       <c r="BC25" s="6">
         <f t="shared" si="20"/>
-        <v>3842</v>
+        <v>3844</v>
       </c>
       <c r="BD25" s="14">
-        <v>8389</v>
+        <v>8391</v>
       </c>
       <c r="BE25" s="7">
         <f t="shared" si="21"/>
-        <v>0.52774282838449926</v>
+        <v>0.52786864620030194</v>
       </c>
       <c r="BF25" s="13">
         <v>26706</v>
@@ -4652,14 +4652,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>7389</v>
+        <v>7393</v>
       </c>
       <c r="BI25" s="15">
-        <v>17616</v>
+        <v>17620</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.6596270501011009</v>
+        <v>0.65977682917696401</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>40079</v>
+        <v>40080</v>
       </c>
       <c r="F26" s="14">
-        <v>48340</v>
+        <v>48341</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>0.43153778856969416</v>
+        <v>0.43154671570640435</v>
       </c>
       <c r="H26" s="13">
         <v>109409</v>
@@ -4694,14 +4694,14 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>39829</v>
+        <v>39830</v>
       </c>
       <c r="K26" s="14">
-        <v>48658</v>
+        <v>48659</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>0.44473489383871528</v>
+        <v>0.44474403385461891</v>
       </c>
       <c r="M26" s="13">
         <v>161175</v>
@@ -4728,14 +4728,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>40749</v>
+        <v>40750</v>
       </c>
       <c r="U26" s="14">
-        <v>49534</v>
+        <v>49535</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.48000387615679052</v>
+        <v>0.48001356654876692</v>
       </c>
       <c r="W26" s="13">
         <v>101010</v>
@@ -4745,14 +4745,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>40870</v>
+        <v>40871</v>
       </c>
       <c r="Z26" s="14">
-        <v>49982</v>
+        <v>49983</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.49482229482229484</v>
+        <v>0.49483219483219482</v>
       </c>
       <c r="AB26" s="13">
         <v>167059</v>
@@ -4762,14 +4762,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>96140</v>
+        <v>96141</v>
       </c>
       <c r="AE26" s="15">
-        <v>119666</v>
+        <v>119667</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.71630980671499289</v>
+        <v>0.71631579262416267</v>
       </c>
       <c r="AG26" s="13">
         <v>98900</v>
@@ -4779,14 +4779,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>42355</v>
+        <v>42356</v>
       </c>
       <c r="AJ26" s="14">
-        <v>50963</v>
+        <v>50964</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.51529828109201214</v>
+        <v>0.51530839231547021</v>
       </c>
       <c r="AL26" s="13">
         <v>94250</v>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="AO26" s="14">
-        <v>53052</v>
+        <v>53053</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.56288594164456229</v>
+        <v>0.56289655172413788</v>
       </c>
       <c r="AQ26" s="13">
         <v>146205</v>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>62925</v>
+        <v>62927</v>
       </c>
       <c r="AT26" s="15">
-        <v>120763</v>
+        <v>120765</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.82598406347252151</v>
+        <v>0.82599774289524985</v>
       </c>
       <c r="AV26" s="13">
         <v>71728</v>
@@ -4830,14 +4830,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>33623</v>
+        <v>33624</v>
       </c>
       <c r="AY26" s="14">
-        <v>51516</v>
+        <v>51517</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71821325005576619</v>
+        <v>0.71822719161275927</v>
       </c>
       <c r="BA26" s="13">
         <v>70808</v>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>21397</v>
+        <v>21399</v>
       </c>
       <c r="BD26" s="14">
-        <v>51521</v>
+        <v>51523</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.72761552366964188</v>
+        <v>0.72764376906564232</v>
       </c>
       <c r="BF26" s="13">
         <v>145908</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>57957</v>
+        <v>57960</v>
       </c>
       <c r="BI26" s="15">
-        <v>119812</v>
+        <v>119815</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.82114757244290926</v>
+        <v>0.82116813334429917</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>303568</v>
+        <v>303569</v>
       </c>
       <c r="P27" s="15">
-        <v>504385</v>
+        <v>504386</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.84995719755183474</v>
+        <v>0.84995888268758935</v>
       </c>
       <c r="R27" s="13">
         <v>274036</v>
@@ -4957,14 +4957,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>125989</v>
+        <v>125990</v>
       </c>
       <c r="Z27" s="14">
-        <v>177091</v>
+        <v>177092</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.65908058981592443</v>
+        <v>0.65908431152165659</v>
       </c>
       <c r="AB27" s="13">
         <v>607620</v>
@@ -5025,14 +5025,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>208702</v>
+        <v>208703</v>
       </c>
       <c r="AT27" s="15">
-        <v>521684</v>
+        <v>521685</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.85334231902928315</v>
+        <v>0.8533439547749051</v>
       </c>
       <c r="AV27" s="13">
         <v>246718</v>
@@ -5076,14 +5076,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>179902</v>
+        <v>179903</v>
       </c>
       <c r="BI27" s="15">
-        <v>515501</v>
+        <v>515502</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.84283834048640915</v>
+        <v>0.84283997547516865</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="E28" s="6">
         <f t="shared" si="0"/>
-        <v>39751</v>
+        <v>39752</v>
       </c>
       <c r="F28" s="14">
-        <v>50902</v>
+        <v>50903</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="1"/>
-        <v>0.57254372644958096</v>
+        <v>0.57255497441088798</v>
       </c>
       <c r="H28" s="13">
         <v>85852</v>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="O28" s="6">
         <f t="shared" si="4"/>
-        <v>85479</v>
+        <v>85482</v>
       </c>
       <c r="P28" s="15">
-        <v>124080</v>
+        <v>124083</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="5"/>
-        <v>0.82830440587449938</v>
+        <v>0.82832443257676902</v>
       </c>
       <c r="R28" s="13">
         <v>79004</v>
@@ -5152,14 +5152,14 @@
       </c>
       <c r="T28" s="6">
         <f t="shared" si="6"/>
-        <v>40795</v>
+        <v>40797</v>
       </c>
       <c r="U28" s="14">
-        <v>51856</v>
+        <v>51858</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="7"/>
-        <v>0.65637182927446713</v>
+        <v>0.65639714444838237</v>
       </c>
       <c r="W28" s="13">
         <v>76321</v>
@@ -5169,14 +5169,14 @@
       </c>
       <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>40929</v>
+        <v>40930</v>
       </c>
       <c r="Z28" s="14">
-        <v>52250</v>
+        <v>52251</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="9"/>
-        <v>0.68460843018304263</v>
+        <v>0.68462153273673043</v>
       </c>
       <c r="AB28" s="13">
         <v>151326</v>
@@ -5186,14 +5186,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>97402</v>
+        <v>97404</v>
       </c>
       <c r="AE28" s="15">
-        <v>127610</v>
+        <v>127612</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.8432787491904894</v>
+        <v>0.84329196568996734</v>
       </c>
       <c r="AG28" s="13">
         <v>73311</v>
@@ -5220,14 +5220,14 @@
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="14"/>
-        <v>40534</v>
+        <v>40535</v>
       </c>
       <c r="AO28" s="14">
-        <v>53652</v>
+        <v>53653</v>
       </c>
       <c r="AP28" s="7">
         <f t="shared" si="15"/>
-        <v>0.79482089419572755</v>
+        <v>0.79483570857159791</v>
       </c>
       <c r="AQ28" s="13">
         <v>147404</v>
@@ -5237,14 +5237,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>57298</v>
+        <v>57300</v>
       </c>
       <c r="AT28" s="15">
-        <v>129662</v>
+        <v>129664</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.87963691623022444</v>
+        <v>0.87965048438305604</v>
       </c>
       <c r="AV28" s="13">
         <v>63116</v>
@@ -5254,14 +5254,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>31290</v>
+        <v>31291</v>
       </c>
       <c r="AY28" s="14">
-        <v>54049</v>
+        <v>54050</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.8563438747702643</v>
+        <v>0.85635971861334681</v>
       </c>
       <c r="BA28" s="13">
         <v>59716</v>
@@ -5271,14 +5271,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>17481</v>
+        <v>17482</v>
       </c>
       <c r="BD28" s="14">
-        <v>53759</v>
+        <v>53760</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.90024449058878697</v>
+        <v>0.90026123651952572</v>
       </c>
       <c r="BF28" s="13">
         <v>143561</v>
@@ -5288,14 +5288,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>48854</v>
+        <v>48855</v>
       </c>
       <c r="BI28" s="15">
-        <v>128170</v>
+        <v>128171</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.89279121767053726</v>
+        <v>0.89279818335063144</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5313,14 +5313,14 @@
       </c>
       <c r="E29" s="6">
         <f t="shared" si="0"/>
-        <v>57272</v>
+        <v>57273</v>
       </c>
       <c r="F29" s="14">
-        <v>66585</v>
+        <v>66586</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="1"/>
-        <v>0.41049652910496531</v>
+        <v>0.41050269410502693</v>
       </c>
       <c r="H29" s="13">
         <v>149172</v>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="J29" s="6">
         <f t="shared" si="2"/>
-        <v>53953</v>
+        <v>53954</v>
       </c>
       <c r="K29" s="14">
-        <v>66894</v>
+        <v>66895</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="3"/>
-        <v>0.44843536320489102</v>
+        <v>0.44844206687582122</v>
       </c>
       <c r="M29" s="13">
         <v>219769</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>65845</v>
+        <v>65846</v>
       </c>
       <c r="P30" s="15">
-        <v>93527</v>
+        <v>93528</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.89266318612619666</v>
+        <v>0.89267273056989871</v>
       </c>
       <c r="R30" s="13">
         <v>53849</v>
@@ -5610,14 +5610,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>74175</v>
+        <v>74176</v>
       </c>
       <c r="AE30" s="15">
-        <v>95871</v>
+        <v>95872</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.89217182527126881</v>
+        <v>0.89218113123266762</v>
       </c>
       <c r="AG30" s="13">
         <v>51279</v>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>28872</v>
+        <v>28873</v>
       </c>
       <c r="AO30" s="14">
-        <v>39191</v>
+        <v>39192</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.80007757635146171</v>
+        <v>0.80009799118079372</v>
       </c>
       <c r="AQ30" s="13">
         <v>105112</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>41222</v>
+        <v>41224</v>
       </c>
       <c r="AT30" s="15">
-        <v>97366</v>
+        <v>97368</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.92630717710632471</v>
+        <v>0.92632620442956082</v>
       </c>
       <c r="AV30" s="13">
         <v>46049</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>21825</v>
+        <v>21826</v>
       </c>
       <c r="AY30" s="14">
-        <v>39051</v>
+        <v>39052</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.84803144476535863</v>
+        <v>0.84805316076353454</v>
       </c>
       <c r="BA30" s="13">
         <v>45889</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>13566</v>
+        <v>13569</v>
       </c>
       <c r="BD30" s="14">
-        <v>38973</v>
+        <v>38976</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.84928850051210525</v>
+        <v>0.84935387565647535</v>
       </c>
       <c r="BF30" s="13">
         <v>107069</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>37226</v>
+        <v>37230</v>
       </c>
       <c r="BI30" s="15">
-        <v>96269</v>
+        <v>96273</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.89913046726877066</v>
+        <v>0.89916782635496739</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5771,14 +5771,14 @@
       </c>
       <c r="O31" s="6">
         <f t="shared" si="4"/>
-        <v>205768</v>
+        <v>205769</v>
       </c>
       <c r="P31" s="15">
-        <v>318009</v>
+        <v>318010</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="5"/>
-        <v>0.90013586571938065</v>
+        <v>0.90013869625520115</v>
       </c>
       <c r="R31" s="13">
         <v>149791</v>
@@ -5822,14 +5822,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>244295</v>
+        <v>244296</v>
       </c>
       <c r="AE31" s="15">
-        <v>324780</v>
+        <v>324781</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.90217919693329074</v>
+        <v>0.90218197474964934</v>
       </c>
       <c r="AG31" s="13">
         <v>142536</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="AN31" s="6">
         <f t="shared" si="14"/>
-        <v>78244</v>
+        <v>78245</v>
       </c>
       <c r="AO31" s="14">
-        <v>106874</v>
+        <v>106875</v>
       </c>
       <c r="AP31" s="7">
         <f t="shared" si="15"/>
-        <v>0.77444366345171411</v>
+        <v>0.77445090977601616</v>
       </c>
       <c r="AQ31" s="13">
         <v>354752</v>
@@ -5873,14 +5873,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>115106</v>
+        <v>115107</v>
       </c>
       <c r="AT31" s="15">
-        <v>329437</v>
+        <v>329438</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.92864028955439293</v>
+        <v>0.92864310842504061</v>
       </c>
       <c r="AV31" s="13">
         <v>121996</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>114615</v>
+        <v>114617</v>
       </c>
       <c r="BI31" s="15">
-        <v>325343</v>
+        <v>325345</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.92565310663093148</v>
+        <v>0.92565879695226394</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>139160</v>
+        <v>139161</v>
       </c>
       <c r="F32" s="14">
-        <v>250998</v>
+        <v>250999</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.62874620494784617</v>
+        <v>0.62874870993276621</v>
       </c>
       <c r="H32" s="13">
         <v>382894</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>135161</v>
+        <v>135162</v>
       </c>
       <c r="K32" s="14">
-        <v>251290</v>
+        <v>251291</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.65629129733033165</v>
+        <v>0.65629390901920637</v>
       </c>
       <c r="M32" s="13">
         <v>877062</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="O32" s="6">
         <f t="shared" si="4"/>
-        <v>334444</v>
+        <v>334448</v>
       </c>
       <c r="P32" s="15">
-        <v>803173</v>
+        <v>803177</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="5"/>
-        <v>0.91575396038136414</v>
+        <v>0.91575852106236499</v>
       </c>
       <c r="R32" s="13">
         <v>340947</v>
@@ -6017,14 +6017,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>140559</v>
+        <v>140560</v>
       </c>
       <c r="Z32" s="14">
-        <v>253992</v>
+        <v>253993</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.77015115450507132</v>
+        <v>0.77015418669173275</v>
       </c>
       <c r="AB32" s="13">
         <v>884817</v>
@@ -6034,14 +6034,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>442933</v>
+        <v>442940</v>
       </c>
       <c r="AE32" s="15">
-        <v>818574</v>
+        <v>818581</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.92513367170838712</v>
+        <v>0.92514158294879056</v>
       </c>
       <c r="AG32" s="13">
         <v>320380</v>
@@ -6051,14 +6051,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>164325</v>
+        <v>164327</v>
       </c>
       <c r="AJ32" s="14">
-        <v>256050</v>
+        <v>256052</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.79920719146014108</v>
+        <v>0.79921343404706913</v>
       </c>
       <c r="AL32" s="13">
         <v>311565</v>
@@ -6068,14 +6068,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>130391</v>
+        <v>130392</v>
       </c>
       <c r="AO32" s="14">
-        <v>258450</v>
+        <v>258451</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.82952192961340332</v>
+        <v>0.82952513921653592</v>
       </c>
       <c r="AQ32" s="13">
         <v>877839</v>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>171144</v>
+        <v>171147</v>
       </c>
       <c r="AT32" s="15">
-        <v>833016</v>
+        <v>833019</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94893938410118484</v>
+        <v>0.94894280158434519</v>
       </c>
       <c r="AV32" s="13">
         <v>297941</v>
@@ -6119,14 +6119,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>35894</v>
+        <v>35896</v>
       </c>
       <c r="BD32" s="14">
-        <v>260533</v>
+        <v>260535</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.88492355976128767</v>
+        <v>0.88493035293957811</v>
       </c>
       <c r="BF32" s="13">
         <v>893063</v>
@@ -6136,14 +6136,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>159662</v>
+        <v>159667</v>
       </c>
       <c r="BI32" s="15">
-        <v>839715</v>
+        <v>839720</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94026401272922511</v>
+        <v>0.94026961143838672</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
-        <v>222277</v>
+        <v>222283</v>
       </c>
       <c r="F35" s="14">
-        <v>358691</v>
+        <v>358697</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="1"/>
-        <v>0.50863221720714624</v>
+        <v>0.50864072534730942</v>
       </c>
       <c r="H35" s="13">
         <v>678572</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J35" s="6">
         <f t="shared" si="2"/>
-        <v>218744</v>
+        <v>218747</v>
       </c>
       <c r="K35" s="14">
-        <v>358794</v>
+        <v>358797</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="3"/>
-        <v>0.52874860736959384</v>
+        <v>0.52875302841850236</v>
       </c>
       <c r="M35" s="13">
         <v>1405014</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O35" s="6">
         <f t="shared" si="4"/>
-        <v>636003</v>
+        <v>636008</v>
       </c>
       <c r="P35" s="15">
-        <v>1205970</v>
+        <v>1205975</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="5"/>
-        <v>0.85833308422549526</v>
+        <v>0.85833664290889633</v>
       </c>
       <c r="R35" s="13">
         <v>600814</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T35" s="6">
         <f t="shared" si="6"/>
-        <v>231478</v>
+        <v>231479</v>
       </c>
       <c r="U35" s="14">
-        <v>362740</v>
+        <v>362741</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="7"/>
-        <v>0.60374758244648097</v>
+        <v>0.6037492468550999</v>
       </c>
       <c r="W35" s="13">
         <v>577797</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y35" s="6">
         <f t="shared" si="8"/>
-        <v>225110</v>
+        <v>225112</v>
       </c>
       <c r="Z35" s="14">
-        <v>364113</v>
+        <v>364115</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="9"/>
-        <v>0.63017461149850207</v>
+        <v>0.63017807292180472</v>
       </c>
       <c r="AB35" s="13">
         <v>1416919</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD35" s="6">
         <f t="shared" si="10"/>
-        <v>775516</v>
+        <v>775519</v>
       </c>
       <c r="AE35" s="15">
-        <v>1227807</v>
+        <v>1227810</v>
       </c>
       <c r="AF35" s="7">
         <f t="shared" si="11"/>
-        <v>0.86653294930761748</v>
+        <v>0.86653506657755308</v>
       </c>
       <c r="AG35" s="13">
         <v>553324</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI35" s="6">
         <f t="shared" si="12"/>
-        <v>245058</v>
+        <v>245064</v>
       </c>
       <c r="AJ35" s="14">
-        <v>367723</v>
+        <v>367729</v>
       </c>
       <c r="AK35" s="7">
         <f t="shared" si="13"/>
-        <v>0.6645708481829814</v>
+        <v>0.66458169173937875</v>
       </c>
       <c r="AL35" s="13">
         <v>528988</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN35" s="6">
         <f t="shared" si="14"/>
-        <v>217300</v>
+        <v>217305</v>
       </c>
       <c r="AO35" s="14">
-        <v>372204</v>
+        <v>372209</v>
       </c>
       <c r="AP35" s="7">
         <f t="shared" si="15"/>
-        <v>0.7036152048817742</v>
+        <v>0.7036246568920278</v>
       </c>
       <c r="AQ35" s="13">
         <v>1379433</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS35" s="6">
         <f t="shared" si="16"/>
-        <v>367247</v>
+        <v>367255</v>
       </c>
       <c r="AT35" s="15">
-        <v>1242143</v>
+        <v>1242151</v>
       </c>
       <c r="AU35" s="7">
         <f t="shared" si="17"/>
-        <v>0.90047360038508573</v>
+        <v>0.90047939986936665</v>
       </c>
       <c r="AV35" s="13">
         <v>465114</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX35" s="6">
         <f t="shared" si="18"/>
-        <v>150906</v>
+        <v>150912</v>
       </c>
       <c r="AY35" s="14">
-        <v>372279</v>
+        <v>372285</v>
       </c>
       <c r="AZ35" s="7">
         <f t="shared" si="19"/>
-        <v>0.80040377197848267</v>
+        <v>0.80041667204169298</v>
       </c>
       <c r="BA35" s="13">
         <v>457177</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC35" s="6">
         <f t="shared" si="20"/>
-        <v>87748</v>
+        <v>87753</v>
       </c>
       <c r="BD35" s="14">
-        <v>371931</v>
+        <v>371936</v>
       </c>
       <c r="BE35" s="7">
         <f t="shared" si="21"/>
-        <v>0.81353830135811733</v>
+        <v>0.81354923804128376</v>
       </c>
       <c r="BF35" s="13">
         <v>1380633</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH35" s="6">
         <f t="shared" si="22"/>
-        <v>474425</v>
+        <v>474435</v>
       </c>
       <c r="BI35" s="15">
-        <v>1225987</v>
+        <v>1225997</v>
       </c>
       <c r="BJ35" s="7">
         <f t="shared" si="23"/>
-        <v>0.88798906009055267</v>
+        <v>0.88799630314500666</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>256607</v>
+        <v>256613</v>
       </c>
       <c r="F36" s="14">
-        <v>364978</v>
+        <v>364984</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.73410073273703325</v>
+        <v>0.7341128008737331</v>
       </c>
       <c r="H36" s="13">
         <v>485610</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>259097</v>
+        <v>259102</v>
       </c>
       <c r="K36" s="14">
-        <v>366711</v>
+        <v>366716</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.75515537159448942</v>
+        <v>0.7551656679228187</v>
       </c>
       <c r="M36" s="13">
         <v>710827</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>374019</v>
+        <v>374026</v>
       </c>
       <c r="P36" s="15">
-        <v>612201</v>
+        <v>612208</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.86125175323953651</v>
+        <v>0.86126160092399418</v>
       </c>
       <c r="R36" s="13">
         <v>464623</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>276282</v>
+        <v>276287</v>
       </c>
       <c r="U36" s="14">
-        <v>372868</v>
+        <v>372873</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.80251730973283719</v>
+        <v>0.80252807114585378</v>
       </c>
       <c r="W36" s="13">
         <v>451202</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>271119</v>
+        <v>271124</v>
       </c>
       <c r="Z36" s="14">
-        <v>375742</v>
+        <v>375747</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.83275783352024146</v>
+        <v>0.83276891503140504</v>
       </c>
       <c r="AB36" s="13">
         <v>709880</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>427625</v>
+        <v>427630</v>
       </c>
       <c r="AE36" s="15">
-        <v>628855</v>
+        <v>628860</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.88586099058995882</v>
+        <v>0.88586803403392123</v>
       </c>
       <c r="AG36" s="13">
         <v>448411</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>282659</v>
+        <v>282664</v>
       </c>
       <c r="AJ36" s="14">
-        <v>381907</v>
+        <v>381912</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.85168963294834421</v>
+        <v>0.85170078343305589</v>
       </c>
       <c r="AL36" s="13">
         <v>443261</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>260466</v>
+        <v>260470</v>
       </c>
       <c r="AO36" s="14">
-        <v>386329</v>
+        <v>386333</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.871560999050221</v>
+        <v>0.87157002307895348</v>
       </c>
       <c r="AQ36" s="13">
         <v>723207</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>261080</v>
+        <v>261088</v>
       </c>
       <c r="AT36" s="15">
-        <v>644784</v>
+        <v>644792</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.89156216684849565</v>
+        <v>0.89157322868832856</v>
       </c>
       <c r="AV36" s="13">
         <v>443230</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>196229</v>
+        <v>196233</v>
       </c>
       <c r="AY36" s="14">
-        <v>390299</v>
+        <v>390303</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.88057893193150283</v>
+        <v>0.880587956591386</v>
       </c>
       <c r="BA36" s="13">
         <v>443322</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>88469</v>
+        <v>88473</v>
       </c>
       <c r="BD36" s="14">
-        <v>389687</v>
+        <v>389691</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.87901570416085828</v>
+        <v>0.8790247269479069</v>
       </c>
       <c r="BF36" s="13">
         <v>734800</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="22"/>
-        <v>185117</v>
+        <v>185123</v>
       </c>
       <c r="BI36" s="15">
-        <v>637992</v>
+        <v>637998</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="23"/>
-        <v>0.86825258573761566</v>
+        <v>0.86826075122482305</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O39" s="6">
         <f t="shared" si="4"/>
-        <v>164050</v>
+        <v>164051</v>
       </c>
       <c r="P39" s="15">
-        <v>262823</v>
+        <v>262824</v>
       </c>
       <c r="Q39" s="7">
         <f t="shared" si="5"/>
-        <v>0.88817659244440084</v>
+        <v>0.88817997181604047</v>
       </c>
       <c r="R39" s="13">
         <v>189177</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T39" s="6">
         <f t="shared" si="6"/>
-        <v>118727</v>
+        <v>118729</v>
       </c>
       <c r="U39" s="14">
-        <v>149158</v>
+        <v>149160</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="7"/>
-        <v>0.78845737061059218</v>
+        <v>0.78846794272030951</v>
       </c>
       <c r="W39" s="13">
         <v>187045</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y39" s="6">
         <f t="shared" si="8"/>
-        <v>120616</v>
+        <v>120617</v>
       </c>
       <c r="Z39" s="14">
-        <v>150235</v>
+        <v>150236</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="9"/>
-        <v>0.80320243791600954</v>
+        <v>0.80320778422304795</v>
       </c>
       <c r="AB39" s="13">
         <v>301836</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD39" s="6">
         <f t="shared" si="10"/>
-        <v>185931</v>
+        <v>185934</v>
       </c>
       <c r="AE39" s="15">
-        <v>268530</v>
+        <v>268533</v>
       </c>
       <c r="AF39" s="7">
         <f t="shared" si="11"/>
-        <v>0.88965530950582439</v>
+        <v>0.88966524867809005</v>
       </c>
       <c r="AG39" s="13">
         <v>184754</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI39" s="6">
         <f t="shared" si="12"/>
-        <v>115713</v>
+        <v>115714</v>
       </c>
       <c r="AJ39" s="14">
-        <v>152283</v>
+        <v>152284</v>
       </c>
       <c r="AK39" s="7">
         <f t="shared" si="13"/>
-        <v>0.82424737759398981</v>
+        <v>0.82425279019669395</v>
       </c>
       <c r="AL39" s="13">
         <v>180486</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="14"/>
-        <v>98548</v>
+        <v>98549</v>
       </c>
       <c r="AO39" s="14">
-        <v>153974</v>
+        <v>153975</v>
       </c>
       <c r="AP39" s="7">
         <f t="shared" si="15"/>
-        <v>0.85310772026639181</v>
+        <v>0.85311326086233841</v>
       </c>
       <c r="AQ39" s="13">
         <v>302709</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS39" s="6">
         <f t="shared" si="16"/>
-        <v>112543</v>
+        <v>112544</v>
       </c>
       <c r="AT39" s="15">
-        <v>273393</v>
+        <v>273394</v>
       </c>
       <c r="AU39" s="7">
         <f t="shared" si="17"/>
-        <v>0.90315451473197028</v>
+        <v>0.90315781823467423</v>
       </c>
       <c r="AV39" s="13">
         <v>175450</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX39" s="6">
         <f t="shared" si="18"/>
-        <v>78389</v>
+        <v>78390</v>
       </c>
       <c r="AY39" s="14">
-        <v>155024</v>
+        <v>155025</v>
       </c>
       <c r="AZ39" s="7">
         <f t="shared" si="19"/>
-        <v>0.88357936734112286</v>
+        <v>0.88358506697064687</v>
       </c>
       <c r="BA39" s="13">
         <v>174499</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC39" s="6">
         <f t="shared" si="20"/>
-        <v>36479</v>
+        <v>36480</v>
       </c>
       <c r="BD39" s="14">
-        <v>155259</v>
+        <v>155260</v>
       </c>
       <c r="BE39" s="7">
         <f t="shared" si="21"/>
-        <v>0.88974148848990542</v>
+        <v>0.8897472191817718</v>
       </c>
       <c r="BF39" s="13">
         <v>304085</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH39" s="6">
         <f t="shared" si="22"/>
-        <v>83608</v>
+        <v>83610</v>
       </c>
       <c r="BI39" s="15">
-        <v>273294</v>
+        <v>273296</v>
       </c>
       <c r="BJ39" s="7">
         <f t="shared" si="23"/>
-        <v>0.89874212802341447</v>
+        <v>0.89874870513178884</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>374894</v>
+        <v>374916</v>
       </c>
       <c r="F40" s="14">
-        <v>520771</v>
+        <v>520793</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.76433127562956638</v>
+        <v>0.7643635648470225</v>
       </c>
       <c r="H40" s="13">
         <v>679109</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>379449</v>
+        <v>379467</v>
       </c>
       <c r="K40" s="14">
-        <v>523743</v>
+        <v>523761</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.77122082022179062</v>
+        <v>0.77124732553978814</v>
       </c>
       <c r="M40" s="13">
         <v>894344</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>479456</v>
+        <v>479480</v>
       </c>
       <c r="P40" s="15">
-        <v>752552</v>
+        <v>752576</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.84145697852280554</v>
+        <v>0.84148381383449766</v>
       </c>
       <c r="R40" s="13">
         <v>670695</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>398523</v>
+        <v>398541</v>
       </c>
       <c r="U40" s="14">
-        <v>531000</v>
+        <v>531018</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.79171605573323189</v>
+        <v>0.79174289356562966</v>
       </c>
       <c r="W40" s="13">
         <v>664170</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>397010</v>
+        <v>397028</v>
       </c>
       <c r="Z40" s="14">
-        <v>534947</v>
+        <v>534965</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.8054368610446121</v>
+        <v>0.8054639625397112</v>
       </c>
       <c r="AB40" s="13">
         <v>900385</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>541915</v>
+        <v>541946</v>
       </c>
       <c r="AE40" s="15">
-        <v>769391</v>
+        <v>769422</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.85451334706819859</v>
+        <v>0.85454777678437555</v>
       </c>
       <c r="AG40" s="13">
         <v>654051</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>407302</v>
+        <v>407326</v>
       </c>
       <c r="AJ40" s="14">
-        <v>542135</v>
+        <v>542159</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.82888796133634834</v>
+        <v>0.82892465572256602</v>
       </c>
       <c r="AL40" s="13">
         <v>640748</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>372418</v>
+        <v>372439</v>
       </c>
       <c r="AO40" s="14">
-        <v>547362</v>
+        <v>547383</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.85425471480207504</v>
+        <v>0.8542874889972345</v>
       </c>
       <c r="AQ40" s="13">
         <v>877850</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>284056</v>
+        <v>284089</v>
       </c>
       <c r="AT40" s="15">
-        <v>786572</v>
+        <v>786605</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.89602096030073475</v>
+        <v>0.89605855214444385</v>
       </c>
       <c r="AV40" s="13">
         <v>620078</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>257053</v>
+        <v>257073</v>
       </c>
       <c r="AY40" s="14">
-        <v>553899</v>
+        <v>553919</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.89327310435138807</v>
+        <v>0.89330535835814207</v>
       </c>
       <c r="BA40" s="13">
         <v>613352</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>101400</v>
+        <v>101422</v>
       </c>
       <c r="BD40" s="14">
-        <v>555634</v>
+        <v>555656</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.90589742920867622</v>
+        <v>0.9059332976822444</v>
       </c>
       <c r="BF40" s="13">
         <v>876639</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="22"/>
-        <v>217692</v>
+        <v>217742</v>
       </c>
       <c r="BI40" s="15">
-        <v>785723</v>
+        <v>785773</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="23"/>
-        <v>0.89629026315279148</v>
+        <v>0.8963472991733199</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS43" s="6">
         <f t="shared" si="16"/>
-        <v>129102</v>
+        <v>129104</v>
       </c>
       <c r="AT43" s="15">
-        <v>284210</v>
+        <v>284212</v>
       </c>
       <c r="AU43" s="7">
         <f t="shared" si="17"/>
-        <v>0.81148603505085171</v>
+        <v>0.81149174551871039</v>
       </c>
       <c r="AV43" s="13">
         <v>239471</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC43" s="6">
         <f t="shared" si="20"/>
-        <v>50113</v>
+        <v>50114</v>
       </c>
       <c r="BD43" s="14">
-        <v>185999</v>
+        <v>186000</v>
       </c>
       <c r="BE43" s="7">
         <f t="shared" si="21"/>
-        <v>0.78103912355181548</v>
+        <v>0.78104332270946453</v>
       </c>
       <c r="BF43" s="13">
         <v>357819</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH43" s="6">
         <f t="shared" si="22"/>
-        <v>87527</v>
+        <v>87529</v>
       </c>
       <c r="BI43" s="15">
-        <v>282588</v>
+        <v>282590</v>
       </c>
       <c r="BJ43" s="7">
         <f t="shared" si="23"/>
-        <v>0.78975124294685306</v>
+        <v>0.78975683236496663</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>124462</v>
+        <v>124464</v>
       </c>
       <c r="AJ44" s="14">
-        <v>160860</v>
+        <v>160862</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.81398643861957287</v>
+        <v>0.8139965590527275</v>
       </c>
       <c r="AL44" s="13">
         <v>193704</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>115479</v>
+        <v>115480</v>
       </c>
       <c r="AO44" s="14">
-        <v>162834</v>
+        <v>162835</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.84063313096270598</v>
+        <v>0.84063829347870977</v>
       </c>
       <c r="AQ44" s="13">
         <v>286760</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>94941</v>
+        <v>94942</v>
       </c>
       <c r="AT44" s="15">
-        <v>246412</v>
+        <v>246413</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.85929697307853259</v>
+        <v>0.85930046031524621</v>
       </c>
       <c r="AV44" s="13">
         <v>192119</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>83615</v>
+        <v>83616</v>
       </c>
       <c r="AY44" s="14">
-        <v>163488</v>
+        <v>163489</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.85097257428989326</v>
+        <v>0.85097777939714447</v>
       </c>
       <c r="BA44" s="13">
         <v>188319</v>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="E47" s="8">
         <f>F47-D47</f>
-        <v>2360211</v>
+        <v>2360253</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(F9:F46)</f>
-        <v>3455929</v>
+        <v>3455971</v>
       </c>
       <c r="G47" s="9">
         <f>F47/C47</f>
-        <v>0.60009654529337353</v>
+        <v>0.60010383828316072</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(H9:H46)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="J47" s="8">
         <f>K47-I47</f>
-        <v>2353657</v>
+        <v>2353691</v>
       </c>
       <c r="K47" s="10">
         <f>SUM(K9:K46)</f>
-        <v>3468889</v>
+        <v>3468923</v>
       </c>
       <c r="L47" s="9">
         <f>K47/H47</f>
-        <v>0.62339590374991194</v>
+        <v>0.62340201390815786</v>
       </c>
       <c r="M47" s="10">
         <f>SUM(M9:M46)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="O47" s="8">
         <f>P47-N47</f>
-        <v>4976443</v>
+        <v>4976502</v>
       </c>
       <c r="P47" s="10">
         <f>SUM(P9:P46)</f>
-        <v>8855384</v>
+        <v>8855443</v>
       </c>
       <c r="Q47" s="9">
         <f>P47/M47</f>
-        <v>0.8548989086054708</v>
+        <v>0.85490460446638517</v>
       </c>
       <c r="R47" s="10">
         <f>SUM(R9:R46)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="T47" s="8">
         <f>U47-S47</f>
-        <v>2484416</v>
+        <v>2484453</v>
       </c>
       <c r="U47" s="10">
         <f>SUM(U9:U46)</f>
-        <v>3513986</v>
+        <v>3514023</v>
       </c>
       <c r="V47" s="9">
         <f>U47/R47</f>
-        <v>0.68456130822252192</v>
+        <v>0.68456851621037507</v>
       </c>
       <c r="W47" s="10">
         <f>SUM(W9:W46)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="Y47" s="8">
         <f>Z47-X47</f>
-        <v>2446610</v>
+        <v>2446646</v>
       </c>
       <c r="Z47" s="10">
         <f>SUM(Z9:Z46)</f>
-        <v>3535538</v>
+        <v>3535574</v>
       </c>
       <c r="AA47" s="9">
         <f>Z47/W47</f>
-        <v>0.70914056416936078</v>
+        <v>0.70914778486966434</v>
       </c>
       <c r="AB47" s="10">
         <f>SUM(AB9:AB46)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AD47" s="8">
         <f>AE47-AC47</f>
-        <v>5974451</v>
+        <v>5974521</v>
       </c>
       <c r="AE47" s="10">
         <f>SUM(AE9:AE46)</f>
-        <v>9059454</v>
+        <v>9059524</v>
       </c>
       <c r="AF47" s="9">
         <f>AE47/AB47</f>
-        <v>0.86496227639711765</v>
+        <v>0.86496895973138344</v>
       </c>
       <c r="AG47" s="10">
         <f>SUM(AG9:AG46)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AI47" s="8">
         <f>AJ47-AH47</f>
-        <v>2598274</v>
+        <v>2598320</v>
       </c>
       <c r="AJ47" s="10">
         <f>SUM(AJ9:AJ46)</f>
-        <v>3584021</v>
+        <v>3584067</v>
       </c>
       <c r="AK47" s="9">
         <f>AJ47/AG47</f>
-        <v>0.73965113600998522</v>
+        <v>0.73966062924461096</v>
       </c>
       <c r="AL47" s="10">
         <f>SUM(AL9:AL46)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="AN47" s="8">
         <f>AO47-AM47</f>
-        <v>2369312</v>
+        <v>2369354</v>
       </c>
       <c r="AO47" s="10">
         <f>SUM(AO9:AO46)</f>
-        <v>3627394</v>
+        <v>3627436</v>
       </c>
       <c r="AP47" s="9">
         <f>AO47/AL47</f>
-        <v>0.77195102356993361</v>
+        <v>0.77195996165137437</v>
       </c>
       <c r="AQ47" s="10">
         <f>SUM(AQ9:AQ46)</f>
@@ -9271,15 +9271,15 @@
       </c>
       <c r="AS47" s="8">
         <f>AT47-AR47</f>
-        <v>3171130</v>
+        <v>3171212</v>
       </c>
       <c r="AT47" s="10">
         <f>SUM(AT9:AT46)</f>
-        <v>9227012</v>
+        <v>9227094</v>
       </c>
       <c r="AU47" s="9">
         <f>AT47/AQ47</f>
-        <v>0.8897153589529625</v>
+        <v>0.88972326580942196</v>
       </c>
       <c r="AV47" s="10">
         <f>SUM(AV9:AV46)</f>
@@ -9291,15 +9291,15 @@
       </c>
       <c r="AX47" s="8">
         <f>AY47-AW47</f>
-        <v>1737671</v>
+        <v>1737712</v>
       </c>
       <c r="AY47" s="10">
         <f>SUM(AY9:AY46)</f>
-        <v>3650008</v>
+        <v>3650049</v>
       </c>
       <c r="AZ47" s="9">
         <f>AY47/AV47</f>
-        <v>0.817925664389477</v>
+        <v>0.81793485202748761</v>
       </c>
       <c r="BA47" s="10">
         <f>SUM(BA9:BA46)</f>
@@ -9311,15 +9311,15 @@
       </c>
       <c r="BC47" s="8">
         <f>BD47-BB47</f>
-        <v>869256</v>
+        <v>869304</v>
       </c>
       <c r="BD47" s="10">
         <f>SUM(BD9:BD46)</f>
-        <v>3647882</v>
+        <v>3647930</v>
       </c>
       <c r="BE47" s="9">
         <f>BD47/BA47</f>
-        <v>0.83398460004938224</v>
+        <v>0.83399557388592693</v>
       </c>
       <c r="BF47" s="10">
         <f>SUM(BF9:BF46)</f>
@@ -9331,15 +9331,15 @@
       </c>
       <c r="BH47" s="8">
         <f>BI47-BG47</f>
-        <v>2887872</v>
+        <v>2887981</v>
       </c>
       <c r="BI47" s="10">
         <f>SUM(BI9:BI46)</f>
-        <v>9180266</v>
+        <v>9180375</v>
       </c>
       <c r="BJ47" s="9">
         <f>BI47/BF47</f>
-        <v>0.88011106334660305</v>
+        <v>0.88012151316427767</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -9351,13 +9351,13 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="24" t="s">
+      <c r="A59" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -9376,13 +9376,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="AQ7:AU7"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="BA7:BE7"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="AG7:AK7"/>
-    <mergeCell ref="AL7:AP7"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="M7:Q7"/>
@@ -9394,6 +9387,13 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="H7:L7"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="AQ7:AU7"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="BA7:BE7"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="AG7:AK7"/>
+    <mergeCell ref="AL7:AP7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
